--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ULLA OIL ROSALIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ULLA OIL ROSALIA.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>22.6827</v>
+        <v>34.9935</v>
       </c>
       <c r="E2" t="n">
-        <v>28.8963</v>
+        <v>39.9415</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.2137</v>
+        <v>-4.947500000000001</v>
       </c>
       <c r="G2" t="n">
         <v>23.2875</v>
@@ -610,13 +610,13 @@
         <v>56.2083</v>
       </c>
       <c r="S2" t="n">
-        <v>-14.6467</v>
+        <v>-2.3356</v>
       </c>
       <c r="T2" t="n">
-        <v>-15.4083</v>
+        <v>-4.363</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7613999999999999</v>
+        <v>2.0273</v>
       </c>
       <c r="V2" t="n">
         <v>4.641100000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0599</v>
+        <v>9.491399999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>20.0887</v>
+        <v>15.2882</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.0286</v>
+        <v>-5.796500000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-23.5853</v>
+        <v>-6.1609</v>
       </c>
       <c r="H3" t="n">
-        <v>-20.2972</v>
+        <v>-8.2059</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2883</v>
+        <v>2.0451</v>
       </c>
       <c r="J3" t="n">
-        <v>12.261</v>
+        <v>36.6945</v>
       </c>
       <c r="K3" t="n">
-        <v>1.950100000000001</v>
+        <v>17.7587</v>
       </c>
       <c r="L3" t="n">
-        <v>10.3105</v>
+        <v>18.9357</v>
       </c>
       <c r="M3" t="n">
-        <v>-35.8461</v>
+        <v>-42.8552</v>
       </c>
       <c r="N3" t="n">
-        <v>-22.2474</v>
+        <v>-25.9647</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.5988</v>
+        <v>-16.8903</v>
       </c>
       <c r="P3" t="n">
-        <v>17.8221</v>
+        <v>0.3915</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.5015</v>
+        <v>-47.5913</v>
       </c>
       <c r="R3" t="n">
-        <v>41.324</v>
+        <v>47.9826</v>
       </c>
       <c r="S3" t="n">
-        <v>29.2902</v>
+        <v>-1.0728</v>
       </c>
       <c r="T3" t="n">
-        <v>29.2421</v>
+        <v>-3.3215</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0482999999999999</v>
+        <v>2.2486</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.4671</v>
+        <v>16.3336</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0879</v>
+        <v>29.5065</v>
       </c>
       <c r="X3" t="n">
-        <v>-12.5549</v>
+        <v>-13.1729</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9445</v>
+        <v>9.267099999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>18.4582</v>
+        <v>19.4779</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.5137</v>
+        <v>-10.2108</v>
       </c>
       <c r="G4" t="n">
         <v>3.1962</v>
@@ -766,13 +766,13 @@
         <v>19.7806</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0353</v>
+        <v>1.2873</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9776</v>
+        <v>0.04220000000000004</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.05759999999999996</v>
+        <v>1.2449</v>
       </c>
       <c r="V4" t="n">
         <v>17.9057</v>
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1605</v>
+        <v>3.3992</v>
       </c>
       <c r="E5" t="n">
-        <v>0.97</v>
+        <v>1.3958</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1904</v>
+        <v>2.0032</v>
       </c>
       <c r="G5" t="n">
         <v>1.7065</v>
@@ -844,13 +844,13 @@
         <v>3.9168</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2163</v>
+        <v>-0.9776</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0516</v>
+        <v>-0.6258</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1647</v>
+        <v>-0.3518000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0.1241000000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>A. SAAVEDRA NUÑEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2657</v>
+        <v>-0.3295</v>
       </c>
       <c r="E6" t="n">
-        <v>9.4186</v>
+        <v>-0.7212</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.152900000000001</v>
+        <v>0.3917</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7311</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1342999999999994</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5966</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>18.5745</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>10.8504</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7242</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-12.8434</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.7159</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1276</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7625</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-18.0179</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>16.2552</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>9.119399999999999</v>
+        <v>-0.0594</v>
       </c>
       <c r="T6" t="n">
-        <v>7.9787</v>
+        <v>-0.0594</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1406</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-11.822</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8836999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.7057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>P. GOMEZ BEIROA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0819</v>
+        <v>-1.2891</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9599</v>
+        <v>-1.0576</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.8782</v>
+        <v>-0.2315</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.1609</v>
+        <v>-0.295</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.2059</v>
+        <v>-0.0677</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0451</v>
+        <v>-0.2273</v>
       </c>
       <c r="J7" t="n">
-        <v>36.6945</v>
+        <v>0.0404</v>
       </c>
       <c r="K7" t="n">
-        <v>17.7587</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18.9357</v>
+        <v>0.0404</v>
       </c>
       <c r="M7" t="n">
-        <v>-42.8552</v>
+        <v>-0.3354</v>
       </c>
       <c r="N7" t="n">
-        <v>-25.9647</v>
+        <v>-0.0677</v>
       </c>
       <c r="O7" t="n">
-        <v>-16.8903</v>
+        <v>-0.2677</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3915</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-47.5913</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>47.9826</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-9.4826</v>
+        <v>-0.0149</v>
       </c>
       <c r="T7" t="n">
-        <v>-10.6497</v>
+        <v>0.077</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1668</v>
+        <v>-0.0919</v>
       </c>
       <c r="V7" t="n">
-        <v>16.3336</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>29.5065</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.1729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SAAVEDRA NUÑEZ</t>
+          <t>A. VAZQUEZ SEIJAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,43 +1030,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3889</v>
+        <v>-1.7217</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7806</v>
+        <v>0.3001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3917</v>
+        <v>-2.0218</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-1.2634</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-1.8901</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.6266</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.4259</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.9718</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.5457</v>
       </c>
       <c r="P8" t="n">
         <v>0.3917</v>
@@ -1078,13 +1078,13 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1188</v>
+        <v>-0.8500000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>0.1376</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.9876</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GOMEZ BEIROA</t>
+          <t>M. SUAREZ MALLON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3158</v>
+        <v>-2.9849</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0576</v>
+        <v>-2.0345</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2582</v>
+        <v>-0.9505</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.295</v>
+        <v>-0.875</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0677</v>
+        <v>-0.2031</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2273</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3354</v>
+        <v>-0.875</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0677</v>
+        <v>-0.2031</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2677</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.7834</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.9792</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-1.1751</v>
       </c>
       <c r="R9" t="n">
         <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0416</v>
+        <v>-0.11</v>
       </c>
       <c r="T9" t="n">
-        <v>0.077</v>
+        <v>-0.3893</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1186</v>
+        <v>0.2794</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ SEIJAS</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8508</v>
+        <v>-3.182799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1978</v>
+        <v>2.2972</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0486</v>
+        <v>-5.4799</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2634</v>
+        <v>-5.9724</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8901</v>
+        <v>1.8308</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6266</v>
+        <v>-7.8031</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1625</v>
+        <v>7.615</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08169999999999999</v>
+        <v>10.1679</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0808</v>
+        <v>-2.5528</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4259</v>
+        <v>-13.5871</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9718</v>
+        <v>-8.3369</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5457</v>
+        <v>-5.2503</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3917</v>
+        <v>7.8339</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-6.071</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3917</v>
+        <v>13.9051</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9791</v>
+        <v>-1.3116</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0353</v>
+        <v>-1.1163</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0144</v>
+        <v>-0.1954</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-3.733</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.869899999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-5.6029</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>I. FERNANDEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7403</v>
+        <v>-3.8607</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7398</v>
+        <v>-1.2281</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.4804</v>
+        <v>-2.633</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.9724</v>
+        <v>3.079899999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8308</v>
+        <v>2.2724</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.8031</v>
+        <v>0.8075999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>7.615</v>
+        <v>11.9301</v>
       </c>
       <c r="K11" t="n">
-        <v>10.1679</v>
+        <v>7.682399999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5528</v>
+        <v>4.247599999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.5871</v>
+        <v>-8.850099999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.3369</v>
+        <v>-5.4102</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.2503</v>
+        <v>-3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8339</v>
+        <v>-6.267</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.071</v>
+        <v>-22.7185</v>
       </c>
       <c r="R11" t="n">
-        <v>13.9051</v>
+        <v>16.4511</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8690999999999998</v>
+        <v>-3.2884</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3263999999999999</v>
+        <v>-2.1573</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1957</v>
+        <v>-1.131</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.733</v>
+        <v>2.6149</v>
       </c>
       <c r="W11" t="n">
-        <v>1.869899999999999</v>
+        <v>11.718</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.6029</v>
+        <v>-9.1031</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SUAREZ MALLON</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0827</v>
+        <v>-3.8846</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2392</v>
+        <v>4.5723</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8435</v>
+        <v>-8.456899999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.875</v>
+        <v>5.7311</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2031</v>
+        <v>0.1342999999999994</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6719000000000001</v>
+        <v>5.5966</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>18.5745</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10.8504</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7.7242</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.875</v>
+        <v>-12.8434</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2031</v>
+        <v>-10.7159</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-2.1276</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7834</v>
+        <v>-1.7625</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>-18.0179</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1958</v>
+        <v>16.2552</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2077</v>
+        <v>3.969</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.594</v>
+        <v>3.1322</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3863</v>
+        <v>0.8366000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2166</v>
+        <v>-11.822</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6659</v>
+        <v>0.8836999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5507</v>
+        <v>-12.7057</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MUÑOZ</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.291399999999999</v>
+        <v>-4.658100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8426</v>
+        <v>-0.3656999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4489</v>
+        <v>-4.2925</v>
       </c>
       <c r="G13" t="n">
-        <v>3.079899999999999</v>
+        <v>-23.5853</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2724</v>
+        <v>-20.2972</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8075999999999999</v>
+        <v>-3.2883</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9301</v>
+        <v>12.261</v>
       </c>
       <c r="K13" t="n">
-        <v>7.682399999999999</v>
+        <v>1.950100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.247599999999999</v>
+        <v>10.3105</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.850099999999999</v>
+        <v>-35.8461</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.4102</v>
+        <v>-22.2474</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.44</v>
+        <v>-13.5988</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.267</v>
+        <v>17.8221</v>
       </c>
       <c r="Q13" t="n">
-        <v>-22.7185</v>
+        <v>-23.5015</v>
       </c>
       <c r="R13" t="n">
-        <v>16.4511</v>
+        <v>41.324</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.7191</v>
+        <v>11.572</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.7719</v>
+        <v>8.787899999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9469</v>
+        <v>2.7841</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6149</v>
+        <v>-10.4671</v>
       </c>
       <c r="W13" t="n">
-        <v>11.718</v>
+        <v>2.0879</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.1031</v>
+        <v>-12.5549</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERMO ANTELO</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.3223</v>
+        <v>-9.193999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.390499999999999</v>
+        <v>-0.06280000000000086</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9317</v>
+        <v>-9.1311</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.8858</v>
+        <v>-5.349900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.1109</v>
+        <v>-19.6197</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.775</v>
+        <v>14.27</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.5859</v>
+        <v>34.1554</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1893</v>
+        <v>7.5721</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.3967</v>
+        <v>26.5839</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2999</v>
+        <v>-39.5054</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.9218</v>
+        <v>-27.1917</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3783000000000001</v>
+        <v>-12.3136</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7835000000000001</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.3294</v>
+        <v>-47.7867</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5459</v>
+        <v>46.6117</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0008</v>
+        <v>0.1676</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8092</v>
+        <v>-3.5537</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1915</v>
+        <v>3.7214</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6521</v>
+        <v>-2.8367</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>17.1227</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9861999999999999</v>
+        <v>-19.9593</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>J. HERMO ANTELO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.8775</v>
+        <v>-11.3429</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.922699999999999</v>
+        <v>-8.5983</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.9548</v>
+        <v>-2.7445</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.349900000000001</v>
+        <v>-7.8858</v>
       </c>
       <c r="H15" t="n">
-        <v>-19.6197</v>
+        <v>-4.1109</v>
       </c>
       <c r="I15" t="n">
-        <v>14.27</v>
+        <v>-3.775</v>
       </c>
       <c r="J15" t="n">
-        <v>34.1554</v>
+        <v>-4.5859</v>
       </c>
       <c r="K15" t="n">
-        <v>7.5721</v>
+        <v>-1.1893</v>
       </c>
       <c r="L15" t="n">
-        <v>26.5839</v>
+        <v>-3.3967</v>
       </c>
       <c r="M15" t="n">
-        <v>-39.5054</v>
+        <v>-3.2999</v>
       </c>
       <c r="N15" t="n">
-        <v>-27.1917</v>
+        <v>-2.9218</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.3136</v>
+        <v>-0.3783000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1751</v>
+        <v>-0.7835000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-47.7867</v>
+        <v>-3.3294</v>
       </c>
       <c r="R15" t="n">
-        <v>46.6117</v>
+        <v>2.5459</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.515599999999999</v>
+        <v>-1.0215</v>
       </c>
       <c r="T15" t="n">
-        <v>-13.4134</v>
+        <v>-0.01709999999999995</v>
       </c>
       <c r="U15" t="n">
-        <v>4.8979</v>
+        <v>-1.0043</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.8367</v>
+        <v>-1.6521</v>
       </c>
       <c r="W15" t="n">
-        <v>17.1227</v>
+        <v>-0.6659</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.9593</v>
+        <v>-0.9861999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.7283</v>
+        <v>-19.0364</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.9727</v>
+        <v>-9.7646</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.755699999999999</v>
+        <v>-9.271599999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-6.8596</v>
@@ -1702,13 +1702,13 @@
         <v>11.3588</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.0755</v>
+        <v>-1.3835</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6382</v>
+        <v>0.5698</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4373</v>
+        <v>-1.9534</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7839</v>
@@ -1735,13 +1735,13 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-23.0353</v>
+        <v>-21.9002</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.888</v>
+        <v>-13.5548</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.1474</v>
+        <v>-8.345499999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-8.4588</v>
@@ -1780,13 +1780,13 @@
         <v>11.9465</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8643999999999998</v>
+        <v>0.2707000000000002</v>
       </c>
       <c r="T17" t="n">
-        <v>2.386</v>
+        <v>1.7191</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.2505</v>
+        <v>-1.4484</v>
       </c>
       <c r="V17" t="n">
         <v>-8.424099999999999</v>
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-32.59</v>
+        <v>-25.5794</v>
       </c>
       <c r="E18" t="n">
-        <v>-19.5372</v>
+        <v>-14.1764</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.053</v>
+        <v>-11.4027</v>
       </c>
       <c r="G18" t="n">
         <v>-23.1148</v>
@@ -1858,13 +1858,13 @@
         <v>25.2641</v>
       </c>
       <c r="S18" t="n">
-        <v>-12.02</v>
+        <v>-5.009</v>
       </c>
       <c r="T18" t="n">
-        <v>-8.3956</v>
+        <v>-3.035</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.6243</v>
+        <v>-1.9739</v>
       </c>
       <c r="V18" t="n">
         <v>-5.877299999999999</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-38.3582</v>
+        <v>-38.6168</v>
       </c>
       <c r="E19" t="n">
-        <v>-20.5359</v>
+        <v>-23.7149</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.8222</v>
+        <v>-14.9018</v>
       </c>
       <c r="G19" t="n">
         <v>-41.2116</v>
@@ -1936,13 +1936,13 @@
         <v>46.6117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8984999999999999</v>
+        <v>-1.1575</v>
       </c>
       <c r="T19" t="n">
-        <v>3.0062</v>
+        <v>-0.1728999999999997</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.9048</v>
+        <v>-0.9845999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-7.606999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-52.3315</v>
+        <v>-50.8838</v>
       </c>
       <c r="E20" t="n">
-        <v>-33.2742</v>
+        <v>-33.3105</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.0571</v>
+        <v>-17.5731</v>
       </c>
       <c r="G20" t="n">
         <v>-30.3884</v>
@@ -2014,13 +2014,13 @@
         <v>20.5637</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4583</v>
+        <v>-0.01039999999999991</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4222</v>
+        <v>0.3858999999999998</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8803</v>
+        <v>-0.3960000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-17.7434</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-166.7178</v>
+        <v>-141.3137</v>
       </c>
       <c r="E21" t="n">
-        <v>-35.71189999999999</v>
+        <v>-25.31639999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-131.0065</v>
+        <v>-115.9963</v>
       </c>
       <c r="G21" t="n">
         <v>-125.0815</v>
@@ -2083,7 +2083,7 @@
         <v>-95.70310000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>16.6466</v>
+        <v>16.64659999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-365.2547000000001</v>
@@ -2092,13 +2092,13 @@
         <v>381.9010999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-26.7398</v>
+        <v>-1.3356</v>
       </c>
       <c r="T21" t="n">
-        <v>-14.3544</v>
+        <v>-3.959599999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-12.3853</v>
+        <v>2.624</v>
       </c>
       <c r="V21" t="n">
         <v>-31.5438</v>
